--- a/backend/data/financials_by_company/1961.HK.xlsx
+++ b/backend/data/financials_by_company/1961.HK.xlsx
@@ -667,590 +667,590 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-85250.948967</v>
+        <v>-3670750</v>
       </c>
       <c r="C2" t="n">
-        <v>0.024462</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-36038000</v>
+        <v>-71428000</v>
       </c>
       <c r="E2" t="n">
-        <v>-3485000</v>
+        <v>-14683000</v>
       </c>
       <c r="F2" t="n">
-        <v>-3485000</v>
+        <v>-14683000</v>
       </c>
       <c r="G2" t="n">
-        <v>-51015000</v>
+        <v>-85056000</v>
       </c>
       <c r="H2" t="n">
-        <v>12221000</v>
+        <v>616000</v>
       </c>
       <c r="I2" t="n">
-        <v>225799000</v>
+        <v>100523000</v>
       </c>
       <c r="J2" t="n">
-        <v>-39523000</v>
+        <v>-86111000</v>
       </c>
       <c r="K2" t="n">
-        <v>-51744000</v>
+        <v>-86727000</v>
       </c>
       <c r="L2" t="n">
-        <v>3282000</v>
+        <v>736000</v>
       </c>
       <c r="M2" t="n">
-        <v>418000</v>
+        <v>56000</v>
       </c>
       <c r="N2" t="n">
-        <v>3700000</v>
+        <v>792000</v>
       </c>
       <c r="O2" t="n">
-        <v>-47615250.948967</v>
+        <v>-74043750</v>
       </c>
       <c r="P2" t="n">
-        <v>-51015000</v>
+        <v>-85056000</v>
       </c>
       <c r="Q2" t="n">
-        <v>297958000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>178023000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>501000</v>
+      </c>
       <c r="S2" t="n">
-        <v>702575958</v>
+        <v>546000000</v>
       </c>
       <c r="T2" t="n">
-        <v>702575958</v>
+        <v>546000000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.073</v>
+        <v>-0.156</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.073</v>
+        <v>-0.156</v>
       </c>
       <c r="W2" t="n">
-        <v>-51015000</v>
+        <v>-85056000</v>
       </c>
       <c r="X2" t="n">
-        <v>-51015000</v>
+        <v>-85056000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-51015000</v>
+        <v>-85056000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-129000</v>
+        <v>1766000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-50886000</v>
+        <v>-86822000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-50886000</v>
+        <v>-86822000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1276000</v>
+        <v>39000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-52162000</v>
+        <v>-86783000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-12453000</v>
+        <v>-10024000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3485000</v>
+        <v>-14683000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-6648000</v>
+        <v>-265000</v>
       </c>
       <c r="AI2" t="n">
-        <v>10133000</v>
+        <v>14948000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3282000</v>
+        <v>736000</v>
       </c>
       <c r="AK2" t="n">
-        <v>418000</v>
+        <v>56000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3700000</v>
+        <v>792000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-39480000</v>
+        <v>-63109000</v>
       </c>
       <c r="AN2" t="n">
-        <v>72159000</v>
+        <v>77500000</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>17967000</v>
+        <v>37358000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>54215000</v>
+        <v>42586000</v>
       </c>
       <c r="AR2" t="n">
-        <v>7921000</v>
+        <v>20370000</v>
       </c>
       <c r="AS2" t="n">
-        <v>46294000</v>
+        <v>22216000</v>
       </c>
       <c r="AT2" t="n">
-        <v>32679000</v>
+        <v>14391000</v>
       </c>
       <c r="AU2" t="n">
-        <v>225799000</v>
+        <v>100523000</v>
       </c>
       <c r="AV2" t="n">
-        <v>258478000</v>
+        <v>114914000</v>
       </c>
       <c r="AW2" t="n">
-        <v>258478000</v>
+        <v>114914000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1585500</v>
+        <v>-5040250</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-43422000</v>
+        <v>-64685000</v>
       </c>
       <c r="E3" t="n">
-        <v>-6342000</v>
+        <v>-20161000</v>
       </c>
       <c r="F3" t="n">
-        <v>-6342000</v>
+        <v>-20161000</v>
       </c>
       <c r="G3" t="n">
-        <v>-53320000</v>
+        <v>-84445000</v>
       </c>
       <c r="H3" t="n">
-        <v>3003000</v>
+        <v>710000</v>
       </c>
       <c r="I3" t="n">
-        <v>225683000</v>
+        <v>87865000</v>
       </c>
       <c r="J3" t="n">
-        <v>-49764000</v>
+        <v>-84846000</v>
       </c>
       <c r="K3" t="n">
-        <v>-52767000</v>
+        <v>-85556000</v>
       </c>
       <c r="L3" t="n">
-        <v>-297000</v>
+        <v>250000</v>
       </c>
       <c r="M3" t="n">
-        <v>312000</v>
+        <v>123000</v>
       </c>
       <c r="N3" t="n">
-        <v>15000</v>
+        <v>373000</v>
       </c>
       <c r="O3" t="n">
-        <v>-48563500</v>
+        <v>-69324250</v>
       </c>
       <c r="P3" t="n">
-        <v>-53320000</v>
+        <v>-84445000</v>
       </c>
       <c r="Q3" t="n">
-        <v>294617000</v>
+        <v>155070000</v>
       </c>
       <c r="R3" t="n">
-        <v>1991000</v>
+        <v>695000</v>
       </c>
       <c r="S3" t="n">
-        <v>591428686</v>
+        <v>546000000</v>
       </c>
       <c r="T3" t="n">
-        <v>591428686</v>
+        <v>546000000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09</v>
+        <v>-0.155</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.09</v>
+        <v>-0.155</v>
       </c>
       <c r="W3" t="n">
-        <v>-53320000</v>
+        <v>-84445000</v>
       </c>
       <c r="X3" t="n">
-        <v>-53320000</v>
+        <v>-84445000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-53320000</v>
+        <v>-84445000</v>
       </c>
       <c r="AA3" t="n">
-        <v>460000</v>
+        <v>1555000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-53780000</v>
+        <v>-86000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53780000</v>
+        <v>-86000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>701000</v>
+        <v>321000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-53079000</v>
+        <v>-85679000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-15667000</v>
+        <v>-13987000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6342000</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>-20161000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-227000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>6342000</v>
+        <v>20388000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-297000</v>
+        <v>250000</v>
       </c>
       <c r="AK3" t="n">
-        <v>312000</v>
+        <v>123000</v>
       </c>
       <c r="AL3" t="n">
-        <v>15000</v>
+        <v>373000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-30737000</v>
+        <v>-51160000</v>
       </c>
       <c r="AN3" t="n">
-        <v>68934000</v>
+        <v>67205000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1242000</v>
+        <v>-113000</v>
       </c>
       <c r="AP3" t="n">
-        <v>25863000</v>
+        <v>37501000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>45017000</v>
+        <v>30121000</v>
       </c>
       <c r="AR3" t="n">
-        <v>7439000</v>
+        <v>6469000</v>
       </c>
       <c r="AS3" t="n">
-        <v>37578000</v>
+        <v>23652000</v>
       </c>
       <c r="AT3" t="n">
-        <v>38197000</v>
+        <v>16045000</v>
       </c>
       <c r="AU3" t="n">
-        <v>225683000</v>
+        <v>87865000</v>
       </c>
       <c r="AV3" t="n">
-        <v>263880000</v>
+        <v>103910000</v>
       </c>
       <c r="AW3" t="n">
-        <v>263880000</v>
+        <v>103910000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-5040250</v>
+        <v>-1585500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-64685000</v>
+        <v>-43422000</v>
       </c>
       <c r="E4" t="n">
-        <v>-20161000</v>
+        <v>-6342000</v>
       </c>
       <c r="F4" t="n">
-        <v>-20161000</v>
+        <v>-6342000</v>
       </c>
       <c r="G4" t="n">
-        <v>-84445000</v>
+        <v>-53320000</v>
       </c>
       <c r="H4" t="n">
-        <v>710000</v>
+        <v>3003000</v>
       </c>
       <c r="I4" t="n">
-        <v>87865000</v>
+        <v>225683000</v>
       </c>
       <c r="J4" t="n">
-        <v>-84846000</v>
+        <v>-49764000</v>
       </c>
       <c r="K4" t="n">
-        <v>-85556000</v>
+        <v>-52767000</v>
       </c>
       <c r="L4" t="n">
-        <v>250000</v>
+        <v>-297000</v>
       </c>
       <c r="M4" t="n">
-        <v>123000</v>
+        <v>312000</v>
       </c>
       <c r="N4" t="n">
-        <v>373000</v>
+        <v>15000</v>
       </c>
       <c r="O4" t="n">
-        <v>-69324250</v>
+        <v>-48563500</v>
       </c>
       <c r="P4" t="n">
-        <v>-84445000</v>
+        <v>-53320000</v>
       </c>
       <c r="Q4" t="n">
-        <v>155070000</v>
+        <v>294617000</v>
       </c>
       <c r="R4" t="n">
-        <v>695000</v>
+        <v>1991000</v>
       </c>
       <c r="S4" t="n">
-        <v>546000000</v>
+        <v>591428686</v>
       </c>
       <c r="T4" t="n">
-        <v>546000000</v>
+        <v>591428686</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.155</v>
+        <v>-0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.155</v>
+        <v>-0.09</v>
       </c>
       <c r="W4" t="n">
-        <v>-84445000</v>
+        <v>-53320000</v>
       </c>
       <c r="X4" t="n">
-        <v>-84445000</v>
+        <v>-53320000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-84445000</v>
+        <v>-53320000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1555000</v>
+        <v>460000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-86000000</v>
+        <v>-53780000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-86000000</v>
+        <v>-53780000</v>
       </c>
       <c r="AD4" t="n">
-        <v>321000</v>
+        <v>701000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-85679000</v>
+        <v>-53079000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13987000</v>
+        <v>-15667000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-20161000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-227000</v>
-      </c>
+        <v>-6342000</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>20388000</v>
+        <v>6342000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>250000</v>
+        <v>-297000</v>
       </c>
       <c r="AK4" t="n">
-        <v>123000</v>
+        <v>312000</v>
       </c>
       <c r="AL4" t="n">
-        <v>373000</v>
+        <v>15000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-51160000</v>
+        <v>-30737000</v>
       </c>
       <c r="AN4" t="n">
-        <v>67205000</v>
+        <v>68934000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-113000</v>
+        <v>-1242000</v>
       </c>
       <c r="AP4" t="n">
-        <v>37501000</v>
+        <v>25863000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30121000</v>
+        <v>45017000</v>
       </c>
       <c r="AR4" t="n">
-        <v>6469000</v>
+        <v>7439000</v>
       </c>
       <c r="AS4" t="n">
-        <v>23652000</v>
+        <v>37578000</v>
       </c>
       <c r="AT4" t="n">
-        <v>16045000</v>
+        <v>38197000</v>
       </c>
       <c r="AU4" t="n">
-        <v>87865000</v>
+        <v>225683000</v>
       </c>
       <c r="AV4" t="n">
-        <v>103910000</v>
+        <v>263880000</v>
       </c>
       <c r="AW4" t="n">
-        <v>103910000</v>
+        <v>263880000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3670750</v>
+        <v>-85250.948967</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.024462</v>
       </c>
       <c r="D5" t="n">
-        <v>-71428000</v>
+        <v>-36038000</v>
       </c>
       <c r="E5" t="n">
-        <v>-14683000</v>
+        <v>-3485000</v>
       </c>
       <c r="F5" t="n">
-        <v>-14683000</v>
+        <v>-3485000</v>
       </c>
       <c r="G5" t="n">
-        <v>-85056000</v>
+        <v>-51015000</v>
       </c>
       <c r="H5" t="n">
-        <v>616000</v>
+        <v>12221000</v>
       </c>
       <c r="I5" t="n">
-        <v>100523000</v>
+        <v>225799000</v>
       </c>
       <c r="J5" t="n">
-        <v>-86111000</v>
+        <v>-39523000</v>
       </c>
       <c r="K5" t="n">
-        <v>-86727000</v>
+        <v>-51744000</v>
       </c>
       <c r="L5" t="n">
-        <v>736000</v>
+        <v>3282000</v>
       </c>
       <c r="M5" t="n">
-        <v>56000</v>
+        <v>418000</v>
       </c>
       <c r="N5" t="n">
-        <v>792000</v>
+        <v>3700000</v>
       </c>
       <c r="O5" t="n">
-        <v>-74043750</v>
+        <v>-47615250.948967</v>
       </c>
       <c r="P5" t="n">
-        <v>-85056000</v>
+        <v>-51015000</v>
       </c>
       <c r="Q5" t="n">
-        <v>178023000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>501000</v>
-      </c>
+        <v>297958000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>546000000</v>
+        <v>702575958</v>
       </c>
       <c r="T5" t="n">
-        <v>546000000</v>
+        <v>702575958</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.156</v>
+        <v>-0.073</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.156</v>
+        <v>-0.073</v>
       </c>
       <c r="W5" t="n">
-        <v>-85056000</v>
+        <v>-51015000</v>
       </c>
       <c r="X5" t="n">
-        <v>-85056000</v>
+        <v>-51015000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-85056000</v>
+        <v>-51015000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1766000</v>
+        <v>-129000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-86822000</v>
+        <v>-50886000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-86822000</v>
+        <v>-50886000</v>
       </c>
       <c r="AD5" t="n">
-        <v>39000</v>
+        <v>-1276000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-86783000</v>
+        <v>-52162000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-10024000</v>
+        <v>-12453000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-14683000</v>
+        <v>-3485000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-265000</v>
+        <v>-6648000</v>
       </c>
       <c r="AI5" t="n">
-        <v>14948000</v>
+        <v>10133000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>736000</v>
+        <v>3282000</v>
       </c>
       <c r="AK5" t="n">
-        <v>56000</v>
+        <v>418000</v>
       </c>
       <c r="AL5" t="n">
-        <v>792000</v>
+        <v>3700000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-63109000</v>
+        <v>-39480000</v>
       </c>
       <c r="AN5" t="n">
-        <v>77500000</v>
+        <v>72159000</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>37358000</v>
+        <v>17967000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>42586000</v>
+        <v>54215000</v>
       </c>
       <c r="AR5" t="n">
-        <v>20370000</v>
+        <v>7921000</v>
       </c>
       <c r="AS5" t="n">
-        <v>22216000</v>
+        <v>46294000</v>
       </c>
       <c r="AT5" t="n">
-        <v>14391000</v>
+        <v>32679000</v>
       </c>
       <c r="AU5" t="n">
-        <v>100523000</v>
+        <v>225799000</v>
       </c>
       <c r="AV5" t="n">
-        <v>114914000</v>
+        <v>258478000</v>
       </c>
       <c r="AW5" t="n">
-        <v>114914000</v>
+        <v>258478000</v>
       </c>
     </row>
   </sheetData>
@@ -1566,694 +1566,694 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>734301174</v>
+        <v>546000000</v>
       </c>
       <c r="C2" t="n">
-        <v>734301174</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2357000</v>
-      </c>
+        <v>546000000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>10919000</v>
+        <v>1200000</v>
       </c>
       <c r="F2" t="n">
-        <v>43472000</v>
+        <v>129212000</v>
       </c>
       <c r="G2" t="n">
-        <v>164164000</v>
+        <v>129212000</v>
       </c>
       <c r="H2" t="n">
-        <v>62234000</v>
+        <v>84241000</v>
       </c>
       <c r="I2" t="n">
-        <v>43472000</v>
+        <v>129212000</v>
       </c>
       <c r="J2" t="n">
-        <v>4699000</v>
+        <v>1200000</v>
       </c>
       <c r="K2" t="n">
-        <v>157944000</v>
+        <v>129212000</v>
       </c>
       <c r="L2" t="n">
-        <v>157944000</v>
+        <v>129212000</v>
       </c>
       <c r="M2" t="n">
-        <v>179254000</v>
+        <v>138513000</v>
       </c>
       <c r="N2" t="n">
-        <v>21310000</v>
+        <v>9301000</v>
       </c>
       <c r="O2" t="n">
-        <v>157944000</v>
+        <v>129212000</v>
       </c>
       <c r="P2" t="n">
-        <v>-205241000</v>
+        <v>-16247000</v>
       </c>
       <c r="Q2" t="n">
-        <v>341146000</v>
+        <v>130168000</v>
       </c>
       <c r="R2" t="n">
-        <v>6650000</v>
+        <v>4946000</v>
       </c>
       <c r="S2" t="n">
-        <v>6650000</v>
+        <v>4946000</v>
       </c>
       <c r="T2" t="n">
-        <v>371369000</v>
+        <v>35409000</v>
       </c>
       <c r="U2" t="n">
-        <v>17397000</v>
+        <v>2841000</v>
       </c>
       <c r="V2" t="n">
-        <v>15601000</v>
+        <v>2164000</v>
       </c>
       <c r="W2" t="n">
-        <v>1796000</v>
+        <v>677000</v>
       </c>
       <c r="X2" t="n">
-        <v>1796000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>677000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>353972000</v>
+        <v>32568000</v>
       </c>
       <c r="AA2" t="n">
-        <v>9123000</v>
+        <v>523000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2903000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6220000</v>
-      </c>
+        <v>523000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>332988000</v>
+        <v>22841000</v>
       </c>
       <c r="AE2" t="n">
-        <v>188070000</v>
+        <v>11674000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15187000</v>
+        <v>753000</v>
       </c>
       <c r="AG2" t="n">
-        <v>129731000</v>
+        <v>10414000</v>
       </c>
       <c r="AH2" t="n">
-        <v>550623000</v>
+        <v>173922000</v>
       </c>
       <c r="AI2" t="n">
-        <v>134417000</v>
+        <v>57113000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6945000</v>
+        <v>21123000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3004000</v>
+        <v>4749000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3004000</v>
+        <v>4749000</v>
       </c>
       <c r="AM2" t="n">
-        <v>296000</v>
+        <v>29414000</v>
       </c>
       <c r="AN2" t="n">
-        <v>296000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>114472000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>53193000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>61279000</v>
-      </c>
+        <v>29414000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>9700000</v>
+        <v>1827000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-4160000</v>
+        <v>-1323000</v>
       </c>
       <c r="AT2" t="n">
-        <v>13860000</v>
+        <v>3150000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4611000</v>
+        <v>1096000</v>
       </c>
       <c r="AV2" t="n">
-        <v>7744000</v>
+        <v>1610000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1505000</v>
+        <v>444000</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>416206000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>116809000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>49948000</v>
+      </c>
       <c r="BA2" t="n">
-        <v>259654000</v>
+        <v>49948000</v>
       </c>
       <c r="BB2" t="n">
-        <v>152689000</v>
+        <v>41596000</v>
       </c>
       <c r="BC2" t="n">
-        <v>-57695000</v>
+        <v>-18755000</v>
       </c>
       <c r="BD2" t="n">
-        <v>210384000</v>
+        <v>60351000</v>
       </c>
       <c r="BE2" t="n">
-        <v>3863000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>25265000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>13137000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>3863000</v>
+        <v>12128000</v>
       </c>
       <c r="BH2" t="n">
-        <v>3863000</v>
+        <v>12128000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>629887174</v>
+        <v>546000000</v>
       </c>
       <c r="C3" t="n">
-        <v>629887174</v>
+        <v>546000000</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>8445000</v>
+        <v>17236000</v>
       </c>
       <c r="F3" t="n">
-        <v>111159000</v>
+        <v>48584000</v>
       </c>
       <c r="G3" t="n">
-        <v>111259000</v>
+        <v>65143000</v>
       </c>
       <c r="H3" t="n">
-        <v>84763000</v>
+        <v>44362000</v>
       </c>
       <c r="I3" t="n">
-        <v>111159000</v>
+        <v>48584000</v>
       </c>
       <c r="J3" t="n">
-        <v>8345000</v>
+        <v>677000</v>
       </c>
       <c r="K3" t="n">
-        <v>111159000</v>
+        <v>48584000</v>
       </c>
       <c r="L3" t="n">
-        <v>111159000</v>
+        <v>65143000</v>
       </c>
       <c r="M3" t="n">
-        <v>116462000</v>
+        <v>54347000</v>
       </c>
       <c r="N3" t="n">
-        <v>5303000</v>
+        <v>5763000</v>
       </c>
       <c r="O3" t="n">
-        <v>111159000</v>
+        <v>48584000</v>
       </c>
       <c r="P3" t="n">
-        <v>-150685000</v>
+        <v>-97365000</v>
       </c>
       <c r="Q3" t="n">
-        <v>244392000</v>
+        <v>130168000</v>
       </c>
       <c r="R3" t="n">
-        <v>5683000</v>
+        <v>4946000</v>
       </c>
       <c r="S3" t="n">
-        <v>5683000</v>
+        <v>4946000</v>
       </c>
       <c r="T3" t="n">
-        <v>111694000</v>
+        <v>61332000</v>
       </c>
       <c r="U3" t="n">
-        <v>7178000</v>
+        <v>18823000</v>
       </c>
       <c r="V3" t="n">
-        <v>2303000</v>
+        <v>2164000</v>
       </c>
       <c r="W3" t="n">
-        <v>4875000</v>
+        <v>16659000</v>
       </c>
       <c r="X3" t="n">
-        <v>4875000</v>
+        <v>100000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>16559000</v>
       </c>
       <c r="Z3" t="n">
-        <v>104516000</v>
+        <v>42509000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3570000</v>
+        <v>577000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3470000</v>
+        <v>577000</v>
       </c>
       <c r="AC3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>77410000</v>
+        <v>35783000</v>
       </c>
       <c r="AE3" t="n">
-        <v>16642000</v>
+        <v>12237000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1493000</v>
+        <v>1425000</v>
       </c>
       <c r="AG3" t="n">
-        <v>59275000</v>
+        <v>22121000</v>
       </c>
       <c r="AH3" t="n">
-        <v>228156000</v>
+        <v>115679000</v>
       </c>
       <c r="AI3" t="n">
-        <v>38877000</v>
+        <v>28808000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13814000</v>
+        <v>115000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6421000</v>
+        <v>8324000</v>
       </c>
       <c r="AL3" t="n">
-        <v>6421000</v>
+        <v>8324000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3961000</v>
+        <v>19053000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3961000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
+        <v>19053000</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>14681000</v>
+        <v>1316000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-2629000</v>
+        <v>-1527000</v>
       </c>
       <c r="AT3" t="n">
-        <v>17310000</v>
+        <v>2843000</v>
       </c>
       <c r="AU3" t="n">
-        <v>7788000</v>
+        <v>590000</v>
       </c>
       <c r="AV3" t="n">
-        <v>8049000</v>
+        <v>1809000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1473000</v>
+        <v>444000</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>189279000</v>
+        <v>86871000</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>67315000</v>
+        <v>39431000</v>
       </c>
       <c r="BB3" t="n">
-        <v>84753000</v>
+        <v>26725000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-45263000</v>
+        <v>-38926000</v>
       </c>
       <c r="BD3" t="n">
-        <v>130016000</v>
+        <v>65651000</v>
       </c>
       <c r="BE3" t="n">
-        <v>37211000</v>
+        <v>20715000</v>
       </c>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>37211000</v>
+        <v>20715000</v>
       </c>
       <c r="BH3" t="n">
-        <v>37211000</v>
+        <v>20715000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>546000000</v>
+        <v>629887174</v>
       </c>
       <c r="C4" t="n">
-        <v>546000000</v>
+        <v>629887174</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>17236000</v>
+        <v>8445000</v>
       </c>
       <c r="F4" t="n">
-        <v>48584000</v>
+        <v>111159000</v>
       </c>
       <c r="G4" t="n">
-        <v>65143000</v>
+        <v>111259000</v>
       </c>
       <c r="H4" t="n">
-        <v>44362000</v>
+        <v>84763000</v>
       </c>
       <c r="I4" t="n">
-        <v>48584000</v>
+        <v>111159000</v>
       </c>
       <c r="J4" t="n">
-        <v>677000</v>
+        <v>8345000</v>
       </c>
       <c r="K4" t="n">
-        <v>48584000</v>
+        <v>111159000</v>
       </c>
       <c r="L4" t="n">
-        <v>65143000</v>
+        <v>111159000</v>
       </c>
       <c r="M4" t="n">
-        <v>54347000</v>
+        <v>116462000</v>
       </c>
       <c r="N4" t="n">
-        <v>5763000</v>
+        <v>5303000</v>
       </c>
       <c r="O4" t="n">
-        <v>48584000</v>
+        <v>111159000</v>
       </c>
       <c r="P4" t="n">
-        <v>-97365000</v>
+        <v>-150685000</v>
       </c>
       <c r="Q4" t="n">
-        <v>130168000</v>
+        <v>244392000</v>
       </c>
       <c r="R4" t="n">
-        <v>4946000</v>
+        <v>5683000</v>
       </c>
       <c r="S4" t="n">
-        <v>4946000</v>
+        <v>5683000</v>
       </c>
       <c r="T4" t="n">
-        <v>61332000</v>
+        <v>111694000</v>
       </c>
       <c r="U4" t="n">
-        <v>18823000</v>
+        <v>7178000</v>
       </c>
       <c r="V4" t="n">
-        <v>2164000</v>
+        <v>2303000</v>
       </c>
       <c r="W4" t="n">
-        <v>16659000</v>
+        <v>4875000</v>
       </c>
       <c r="X4" t="n">
+        <v>4875000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>104516000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3570000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3470000</v>
+      </c>
+      <c r="AC4" t="n">
         <v>100000</v>
       </c>
-      <c r="Y4" t="n">
-        <v>16559000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>42509000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>577000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>577000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
       <c r="AD4" t="n">
-        <v>35783000</v>
+        <v>77410000</v>
       </c>
       <c r="AE4" t="n">
-        <v>12237000</v>
+        <v>16642000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1425000</v>
+        <v>1493000</v>
       </c>
       <c r="AG4" t="n">
-        <v>22121000</v>
+        <v>59275000</v>
       </c>
       <c r="AH4" t="n">
-        <v>115679000</v>
+        <v>228156000</v>
       </c>
       <c r="AI4" t="n">
-        <v>28808000</v>
+        <v>38877000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>115000</v>
+        <v>13814000</v>
       </c>
       <c r="AK4" t="n">
-        <v>8324000</v>
+        <v>6421000</v>
       </c>
       <c r="AL4" t="n">
-        <v>8324000</v>
+        <v>6421000</v>
       </c>
       <c r="AM4" t="n">
-        <v>19053000</v>
+        <v>3961000</v>
       </c>
       <c r="AN4" t="n">
-        <v>19053000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>3961000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" t="n">
-        <v>1316000</v>
+        <v>14681000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1527000</v>
+        <v>-2629000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2843000</v>
+        <v>17310000</v>
       </c>
       <c r="AU4" t="n">
-        <v>590000</v>
+        <v>7788000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1809000</v>
+        <v>8049000</v>
       </c>
       <c r="AW4" t="n">
-        <v>444000</v>
+        <v>1473000</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>86871000</v>
+        <v>189279000</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>39431000</v>
+        <v>67315000</v>
       </c>
       <c r="BB4" t="n">
-        <v>26725000</v>
+        <v>84753000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-38926000</v>
+        <v>-45263000</v>
       </c>
       <c r="BD4" t="n">
-        <v>65651000</v>
+        <v>130016000</v>
       </c>
       <c r="BE4" t="n">
-        <v>20715000</v>
+        <v>37211000</v>
       </c>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>20715000</v>
+        <v>37211000</v>
       </c>
       <c r="BH4" t="n">
-        <v>20715000</v>
+        <v>37211000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>546000000</v>
+        <v>734301174</v>
       </c>
       <c r="C5" t="n">
-        <v>546000000</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>734301174</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2357000</v>
+      </c>
       <c r="E5" t="n">
-        <v>1200000</v>
+        <v>10919000</v>
       </c>
       <c r="F5" t="n">
-        <v>129212000</v>
+        <v>43472000</v>
       </c>
       <c r="G5" t="n">
-        <v>129212000</v>
+        <v>164164000</v>
       </c>
       <c r="H5" t="n">
-        <v>84241000</v>
+        <v>62234000</v>
       </c>
       <c r="I5" t="n">
-        <v>129212000</v>
+        <v>43472000</v>
       </c>
       <c r="J5" t="n">
-        <v>1200000</v>
+        <v>4699000</v>
       </c>
       <c r="K5" t="n">
-        <v>129212000</v>
+        <v>157944000</v>
       </c>
       <c r="L5" t="n">
-        <v>129212000</v>
+        <v>157944000</v>
       </c>
       <c r="M5" t="n">
-        <v>138513000</v>
+        <v>179254000</v>
       </c>
       <c r="N5" t="n">
-        <v>9301000</v>
+        <v>21310000</v>
       </c>
       <c r="O5" t="n">
-        <v>129212000</v>
+        <v>157944000</v>
       </c>
       <c r="P5" t="n">
-        <v>-16247000</v>
+        <v>-205241000</v>
       </c>
       <c r="Q5" t="n">
-        <v>130168000</v>
+        <v>341146000</v>
       </c>
       <c r="R5" t="n">
-        <v>4946000</v>
+        <v>6650000</v>
       </c>
       <c r="S5" t="n">
-        <v>4946000</v>
+        <v>6650000</v>
       </c>
       <c r="T5" t="n">
-        <v>35409000</v>
+        <v>371369000</v>
       </c>
       <c r="U5" t="n">
-        <v>2841000</v>
+        <v>17397000</v>
       </c>
       <c r="V5" t="n">
-        <v>2164000</v>
+        <v>15601000</v>
       </c>
       <c r="W5" t="n">
-        <v>677000</v>
+        <v>1796000</v>
       </c>
       <c r="X5" t="n">
-        <v>677000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>1796000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>32568000</v>
+        <v>353972000</v>
       </c>
       <c r="AA5" t="n">
-        <v>523000</v>
+        <v>9123000</v>
       </c>
       <c r="AB5" t="n">
-        <v>523000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>2903000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6220000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>22841000</v>
+        <v>332988000</v>
       </c>
       <c r="AE5" t="n">
-        <v>11674000</v>
+        <v>188070000</v>
       </c>
       <c r="AF5" t="n">
-        <v>753000</v>
+        <v>15187000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10414000</v>
+        <v>129731000</v>
       </c>
       <c r="AH5" t="n">
-        <v>173922000</v>
+        <v>550623000</v>
       </c>
       <c r="AI5" t="n">
-        <v>57113000</v>
+        <v>134417000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21123000</v>
+        <v>6945000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4749000</v>
+        <v>3004000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4749000</v>
+        <v>3004000</v>
       </c>
       <c r="AM5" t="n">
-        <v>29414000</v>
+        <v>296000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29414000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+        <v>296000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>114472000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>53193000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>61279000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>1827000</v>
+        <v>9700000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1323000</v>
+        <v>-4160000</v>
       </c>
       <c r="AT5" t="n">
-        <v>3150000</v>
+        <v>13860000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1096000</v>
+        <v>4611000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1610000</v>
+        <v>7744000</v>
       </c>
       <c r="AW5" t="n">
-        <v>444000</v>
+        <v>1505000</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>116809000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>49948000</v>
-      </c>
+        <v>416206000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>49948000</v>
+        <v>259654000</v>
       </c>
       <c r="BB5" t="n">
-        <v>41596000</v>
+        <v>152689000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-18755000</v>
+        <v>-57695000</v>
       </c>
       <c r="BD5" t="n">
-        <v>60351000</v>
+        <v>210384000</v>
       </c>
       <c r="BE5" t="n">
-        <v>25265000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13137000</v>
-      </c>
+        <v>3863000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>12128000</v>
+        <v>3863000</v>
       </c>
       <c r="BH5" t="n">
-        <v>12128000</v>
+        <v>3863000</v>
       </c>
     </row>
   </sheetData>
@@ -2509,548 +2509,548 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-55205000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-5685000</v>
-      </c>
+        <v>-26213000</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>11805000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>13292000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-10000</v>
+        <v>-529000</v>
       </c>
       <c r="G2" t="n">
-        <v>3863000</v>
+        <v>12128000</v>
       </c>
       <c r="H2" t="n">
-        <v>37211000</v>
+        <v>47156000</v>
       </c>
       <c r="I2" t="n">
-        <v>2530000</v>
+        <v>-1652000</v>
       </c>
       <c r="J2" t="n">
-        <v>-35878000</v>
+        <v>-33376000</v>
       </c>
       <c r="K2" t="n">
-        <v>15240000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-418000</v>
-      </c>
+        <v>-364000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>13292000</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>13292000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6120000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>6120000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-5685000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>11805000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
-        <v>4077000</v>
+        <v>-7328000</v>
       </c>
       <c r="W2" t="n">
-        <v>4221000</v>
+        <v>-2210000</v>
       </c>
       <c r="X2" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>792000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>13002000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-13002000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-353000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>323000</v>
-      </c>
+        <v>-5400000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>-676000</v>
+        <v>-5400000</v>
       </c>
       <c r="AE2" t="n">
-        <v>200000</v>
+        <v>-510000</v>
       </c>
       <c r="AF2" t="n">
-        <v>210000</v>
+        <v>19000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-10000</v>
+        <v>-529000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-55195000</v>
+        <v>-25684000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-124000</v>
+        <v>-2156000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-33092000</v>
+        <v>44463000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-16332000</v>
+        <v>2769000</v>
       </c>
       <c r="AL2" t="n">
-        <v>277414000</v>
+        <v>4915000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-210899000</v>
+        <v>35375000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-83275000</v>
+        <v>1404000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-52000</v>
+        <v>-1001000</v>
       </c>
       <c r="AP2" t="n">
-        <v>12221000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7087000</v>
-      </c>
+        <v>616000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>5134000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>616000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>111000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>4000</v>
+        <v>23000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-3760000</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-52162000</v>
+        <v>-86783000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-83010000</v>
+        <v>-20358000</v>
       </c>
       <c r="C3" t="n">
-        <v>-35087000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>18706000</v>
+        <v>16027000</v>
       </c>
       <c r="E3" t="n">
-        <v>130736000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-7195000</v>
+        <v>-268000</v>
       </c>
       <c r="G3" t="n">
-        <v>37211000</v>
+        <v>20715000</v>
       </c>
       <c r="H3" t="n">
-        <v>20715000</v>
+        <v>12128000</v>
       </c>
       <c r="I3" t="n">
-        <v>2644000</v>
+        <v>1977000</v>
       </c>
       <c r="J3" t="n">
-        <v>13852000</v>
+        <v>6610000</v>
       </c>
       <c r="K3" t="n">
-        <v>96858000</v>
+        <v>15573000</v>
       </c>
       <c r="L3" t="n">
-        <v>-214000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>130736000</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>130736000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-16381000</v>
+        <v>16027000</v>
       </c>
       <c r="P3" t="n">
-        <v>-16381000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-35087000</v>
-      </c>
+        <v>16027000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>18706000</v>
+        <v>16027000</v>
       </c>
       <c r="S3" t="n">
-        <v>-35087000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-35087000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>18706000</v>
+        <v>16027000</v>
       </c>
       <c r="V3" t="n">
-        <v>-7191000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-11000</v>
-      </c>
+        <v>11127000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>15000</v>
+        <v>373000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>13130000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>13130000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
+        <v>-2163000</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2163000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-7195000</v>
+        <v>-213000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-7195000</v>
+        <v>-268000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-75815000</v>
+        <v>-20090000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-66000</v>
+        <v>-57000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-47889000</v>
+        <v>30062000</v>
       </c>
       <c r="AK3" t="n">
-        <v>14427000</v>
+        <v>-5355000</v>
       </c>
       <c r="AL3" t="n">
-        <v>44091000</v>
+        <v>15215000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-42144000</v>
+        <v>27090000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-64263000</v>
+        <v>-6888000</v>
       </c>
       <c r="AO3" t="n">
-        <v>297000</v>
+        <v>-365000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3003000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
+        <v>710000</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>3003000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>710000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>272000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>10000</v>
+        <v>-13000</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>668000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-53079000</v>
+        <v>-85679000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-20358000</v>
+        <v>-83010000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-35087000</v>
       </c>
       <c r="D4" t="n">
-        <v>16027000</v>
+        <v>18706000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>130736000</v>
       </c>
       <c r="F4" t="n">
-        <v>-268000</v>
+        <v>-7195000</v>
       </c>
       <c r="G4" t="n">
+        <v>37211000</v>
+      </c>
+      <c r="H4" t="n">
         <v>20715000</v>
       </c>
-      <c r="H4" t="n">
-        <v>12128000</v>
-      </c>
       <c r="I4" t="n">
-        <v>1977000</v>
+        <v>2644000</v>
       </c>
       <c r="J4" t="n">
-        <v>6610000</v>
+        <v>13852000</v>
       </c>
       <c r="K4" t="n">
-        <v>15573000</v>
+        <v>96858000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-214000</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>130736000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>130736000</v>
       </c>
       <c r="O4" t="n">
-        <v>16027000</v>
+        <v>-16381000</v>
       </c>
       <c r="P4" t="n">
-        <v>16027000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-16381000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-35087000</v>
+      </c>
       <c r="R4" t="n">
-        <v>16027000</v>
+        <v>18706000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-35087000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-35087000</v>
       </c>
       <c r="U4" t="n">
-        <v>16027000</v>
+        <v>18706000</v>
       </c>
       <c r="V4" t="n">
-        <v>11127000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-7191000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-11000</v>
+      </c>
       <c r="X4" t="n">
-        <v>373000</v>
+        <v>15000</v>
       </c>
       <c r="Y4" t="n">
-        <v>13130000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>13130000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>-2163000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" t="n">
-        <v>-2163000</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-213000</v>
+        <v>-7195000</v>
       </c>
       <c r="AF4" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-268000</v>
+        <v>-7195000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-20090000</v>
+        <v>-75815000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-57000</v>
+        <v>-66000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>30062000</v>
+        <v>-47889000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5355000</v>
+        <v>14427000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15215000</v>
+        <v>44091000</v>
       </c>
       <c r="AM4" t="n">
-        <v>27090000</v>
+        <v>-42144000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-6888000</v>
+        <v>-64263000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-365000</v>
+        <v>297000</v>
       </c>
       <c r="AP4" t="n">
-        <v>710000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>3003000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
       <c r="AR4" t="n">
-        <v>710000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>272000</v>
-      </c>
+        <v>3003000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-13000</v>
+        <v>10000</v>
       </c>
       <c r="AU4" t="n">
-        <v>668000</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>-85679000</v>
+        <v>-53079000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-26213000</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>-55205000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-5685000</v>
+      </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>11805000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>13292000</v>
       </c>
       <c r="F5" t="n">
-        <v>-529000</v>
+        <v>-10000</v>
       </c>
       <c r="G5" t="n">
-        <v>12128000</v>
+        <v>3863000</v>
       </c>
       <c r="H5" t="n">
-        <v>47156000</v>
+        <v>37211000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1652000</v>
+        <v>2530000</v>
       </c>
       <c r="J5" t="n">
-        <v>-33376000</v>
+        <v>-35878000</v>
       </c>
       <c r="K5" t="n">
-        <v>-364000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>15240000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-418000</v>
+      </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>13292000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>13292000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6120000</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>6120000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-5685000</v>
+      </c>
       <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
+        <v>11805000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-7328000</v>
+        <v>4077000</v>
       </c>
       <c r="W5" t="n">
-        <v>-2210000</v>
+        <v>4221000</v>
       </c>
       <c r="X5" t="n">
-        <v>792000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13002000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-13002000</v>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-5400000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>-353000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>323000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>-5400000</v>
+        <v>-676000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-510000</v>
+        <v>200000</v>
       </c>
       <c r="AF5" t="n">
-        <v>19000</v>
+        <v>210000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-529000</v>
+        <v>-10000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-25684000</v>
+        <v>-55195000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2156000</v>
+        <v>-124000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>44463000</v>
+        <v>-33092000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2769000</v>
+        <v>-16332000</v>
       </c>
       <c r="AL5" t="n">
-        <v>4915000</v>
+        <v>277414000</v>
       </c>
       <c r="AM5" t="n">
-        <v>35375000</v>
+        <v>-210899000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1404000</v>
+        <v>-83275000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1001000</v>
+        <v>-52000</v>
       </c>
       <c r="AP5" t="n">
-        <v>616000</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>12221000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7087000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>616000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>111000</v>
-      </c>
+        <v>5134000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>23000</v>
+        <v>4000</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>-3760000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-86783000</v>
+        <v>-52162000</v>
       </c>
     </row>
   </sheetData>
@@ -3560,187 +3560,187 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Qiang  Li', 'age': 37, 'title': 'Chairman of the Board &amp; CEO', 'yearBorn': 1988, 'fiscalYear': 2024, 'totalPay': 1219839, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Le  Wang', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2024, 'totalPay': 1797901, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiding  Zhong', 'age': 32, 'title': 'Senior EVP &amp; Chief Strategy Officer', 'yearBorn': 1993, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai-Yee  Wong ACIS, ACS, BEc, HKICS, HKICS; ICSA, UKICSA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Qiang  Li', 'age': 37, 'title': 'Chairman of the Board &amp; CEO', 'yearBorn': 1988, 'fiscalYear': 2024, 'totalPay': 1218867, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Le  Wang', 'age': 45, 'title': 'Executive Director', 'yearBorn': 1980, 'fiscalYear': 2024, 'totalPay': 1796468, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiding  Zhong', 'age': 32, 'title': 'Senior EVP &amp; Chief Strategy Officer', 'yearBorn': 1993, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Wai-Yee  Wong ACIS, ACS, BEc, HKICS, HKICS; ICSA, UKICSA', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.482</v>
+        <v>0.532</v>
       </c>
       <c r="AD2" t="n">
         <v>116668001</v>
@@ -3872,7 +3872,7 @@
         <v>116668001</v>
       </c>
       <c r="AF2" t="n">
-        <v>2757200</v>
+        <v>2369796</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -3908,10 +3908,10 @@
         <v>0.5063229</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.14532</v>
+        <v>0.099</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.2586</v>
+        <v>0.247565</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3949,10 +3949,10 @@
         <v>734301174</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.19456781</v>
+        <v>0.19446458</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5088200000000001</v>
+        <v>0.5090901</v>
       </c>
       <c r="BG2" t="n">
         <v>1735603200</v>
@@ -3976,10 +3976,10 @@
         <v>-2.155</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.7324324</v>
+        <v>-0.74615383</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="n">
         <v>0.0252</v>
@@ -4092,140 +4092,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
+      <c r="CU2" t="n">
+        <v>-0.151</v>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
+          <t>0.072 - 0.255</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>2369796</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.027000003</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.37500006</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>0.072 - 0.59</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.49099997</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>-0.8322034</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-74.61539</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1743168054</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1743168054</v>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1584408600000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-60.399998</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.148565</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.600105</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CW2" t="n">
+      <c r="DU2" t="n">
         <v>1774943991</v>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>finmb_655380516</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DZ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="inlineStr">
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>INFINITIES TECH</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
         <is>
           <t>Infinities Technology International (Cayman) Holding Limited</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>INFINITIES TECH</t>
-        </is>
-      </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>1584408600000</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.151</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>0.072 - 0.255</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>2757200</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.027000003</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.37500006</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>0.072 - 0.59</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.49099997</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.8322034</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-73.24324</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1743168054</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1743168054</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.04632</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.31874484</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.15959999</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.6171693</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-60.399998</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.099</v>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
